--- a/cds/mm_australia-5year-cds.xlsx
+++ b/cds/mm_australia-5year-cds.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="483">
   <si>
     <t>Date</t>
   </si>
@@ -1449,6 +1449,21 @@
   </si>
   <si>
     <t>2026-03-06</t>
+  </si>
+  <si>
+    <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
   </si>
 </sst>
 </file>
@@ -1798,7 +1813,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B477"/>
+  <dimension ref="A1:B482"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -5615,6 +5630,46 @@
       </c>
       <c r="B477" s="3">
         <v>14.2418</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2">
+      <c r="A478" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B478" s="3">
+        <v>15.2932</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2">
+      <c r="A479" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B479" s="3">
+        <v>16.2798</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2">
+      <c r="A480" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="B480" s="3">
+        <v>16.606</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2">
+      <c r="A481" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="B481" s="3">
+        <v>16.3548</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2">
+      <c r="A482" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B482" s="3">
+        <v>15.8189</v>
       </c>
     </row>
   </sheetData>
